--- a/dashboard-financeiro-pme/dashboard/dashboard_financeiro.xlsx
+++ b/dashboard-financeiro-pme/dashboard/dashboard_financeiro.xlsx
@@ -424,12 +424,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Fluxo Mensal'!$A$5:$A$16</f>
+              <f>'Fluxo Mensal'!$A$5:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Fluxo Mensal'!$B$5:$B$16</f>
+              <f>'Fluxo Mensal'!$B$5:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -451,12 +451,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Fluxo Mensal'!$A$5:$A$16</f>
+              <f>'Fluxo Mensal'!$A$5:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Fluxo Mensal'!$C$5:$C$16</f>
+              <f>'Fluxo Mensal'!$C$5:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -552,12 +552,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Fluxo Mensal'!$A$5:$A$16</f>
+              <f>'Fluxo Mensal'!$A$5:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Fluxo Mensal'!$B$5:$B$16</f>
+              <f>'Fluxo Mensal'!$B$5:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -579,12 +579,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Fluxo Mensal'!$A$5:$A$16</f>
+              <f>'Fluxo Mensal'!$A$5:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Fluxo Mensal'!$C$5:$C$16</f>
+              <f>'Fluxo Mensal'!$C$5:$C$11</f>
             </numRef>
           </val>
         </ser>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Fluxo Mensal'!$A$5:$A$16</f>
+              <f>'Fluxo Mensal'!$A$5:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Fluxo Mensal'!$E$5:$E$16</f>
+              <f>'Fluxo Mensal'!$E$5:$E$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1311,7 +1311,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: Jan/2026 a Dec/2026 · dados tratados a partir de um export bruto simulado (ver README)</t>
+          <t>Período: Mar/2026 a Sep/2026 · dados tratados a partir de um export bruto simulado (ver README)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1348,19 +1348,19 @@
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7">
-        <f>'Fluxo Mensal'!B17</f>
+        <f>'Fluxo Mensal'!B12</f>
         <v/>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="10">
-        <f>'Fluxo Mensal'!C17</f>
+        <f>'Fluxo Mensal'!C12</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="11">
-        <f>'Fluxo Mensal'!D17</f>
+        <f>'Fluxo Mensal'!D12</f>
         <v/>
       </c>
       <c r="H5" s="8" t="n"/>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46026</v>
+        <v>46109</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>2072.16</v>
+        <v>1195.81</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1525,11 +1525,11 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46026</v>
+        <v>46109</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1539,25 +1539,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>603.78</v>
+        <v>4177.04</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46027</v>
+        <v>46110</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1571,17 +1571,17 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>4369.96</v>
+        <v>1370.69</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46028</v>
+        <v>46111</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>1430.69</v>
+        <v>2789.13</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1609,53 +1609,53 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46029</v>
+        <v>46112</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>172.69</v>
+        <v>2246.21</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46029</v>
+        <v>46113</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1210.74</v>
+        <v>426.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1665,44 +1665,44 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46059</v>
+        <v>46113</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>4333.04</v>
+        <v>603.78</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46061</v>
+        <v>46113</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>4740.57</v>
+        <v>2072.16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1721,16 +1721,16 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46061</v>
+        <v>46116</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>1444.69</v>
+        <v>1713.84</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,16 +1749,16 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46086</v>
+        <v>46117</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E11" s="16" t="n">
-        <v>801.05</v>
+        <v>2995.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1777,35 +1777,35 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46087</v>
+        <v>46117</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>849.83</v>
+        <v>4997.88</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46087</v>
+        <v>46118</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1823,26 +1823,26 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>2351.69</v>
+        <v>2025.01</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46088</v>
+        <v>46118</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1851,26 +1851,26 @@
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>3351.12</v>
+        <v>1699.88</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46089</v>
+        <v>46119</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4676.8</v>
+        <v>2324.87</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1889,25 +1889,25 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46109</v>
+        <v>46119</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E16" s="16" t="n">
-        <v>4177.04</v>
+        <v>999.61</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1917,16 +1917,16 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46109</v>
+        <v>46121</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1935,26 +1935,26 @@
         </is>
       </c>
       <c r="E17" s="16" t="n">
-        <v>1195.81</v>
+        <v>4890.83</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46110</v>
+        <v>46123</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1963,26 +1963,26 @@
         </is>
       </c>
       <c r="E18" s="16" t="n">
-        <v>1370.69</v>
+        <v>3682.29</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46111</v>
+        <v>46123</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="E19" s="16" t="n">
-        <v>2789.13</v>
+        <v>2828.16</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2001,25 +2001,25 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46112</v>
+        <v>46123</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E20" s="16" t="n">
-        <v>2246.21</v>
+        <v>4942.65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2029,16 +2029,16 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46113</v>
+        <v>46123</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>426.18</v>
+        <v>2378.98</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2057,44 +2057,44 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46116</v>
+        <v>46124</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E22" s="16" t="n">
-        <v>1713.84</v>
+        <v>3383.15</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2103,39 +2103,39 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4641.98</v>
+        <v>2304.31</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E24" s="16" t="n">
-        <v>2304.31</v>
+        <v>4772.99</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
@@ -2197,16 +2197,16 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4772.99</v>
+        <v>4601.73</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2225,16 +2225,16 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E28" s="16" t="n">
-        <v>4601.73</v>
+        <v>1561.63</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46131</v>
+        <v>46133</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2267,11 +2267,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E29" s="16" t="n">
-        <v>1561.63</v>
+        <v>916.59</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2299,39 +2299,39 @@
         </is>
       </c>
       <c r="E30" s="16" t="n">
-        <v>916.59</v>
+        <v>4867.08</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4867.08</v>
+        <v>4258.95</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
@@ -2365,16 +2365,16 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2383,11 +2383,11 @@
         </is>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4258.95</v>
+        <v>2351.13</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
@@ -2421,35 +2421,35 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E35" s="16" t="n">
-        <v>2351.13</v>
+        <v>2513.45</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2467,11 +2467,11 @@
         </is>
       </c>
       <c r="E36" s="16" t="n">
-        <v>2513.45</v>
+        <v>1956.72</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>1956.72</v>
+        <v>4290.82</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2509,21 +2509,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E38" s="16" t="n">
-        <v>2881.02</v>
+        <v>4647.99</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2537,35 +2537,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>4290.82</v>
+        <v>2881.02</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="E40" s="16" t="n">
-        <v>4647.99</v>
+        <v>4369.96</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2589,29 +2589,29 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E41" s="16" t="n">
-        <v>3354.51</v>
+        <v>801.05</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
@@ -2621,31 +2621,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E42" s="16" t="n">
-        <v>2995.42</v>
+        <v>3354.51</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E43" s="16" t="n">
-        <v>4997.88</v>
+        <v>3355.92</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2677,49 +2677,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E44" s="16" t="n">
-        <v>3746.49</v>
+        <v>2776.65</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E45" s="16" t="n">
-        <v>4089.32</v>
+        <v>2243.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2729,16 +2729,16 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46157</v>
+        <v>46149</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2747,119 +2747,119 @@
         </is>
       </c>
       <c r="E46" s="16" t="n">
-        <v>2801.17</v>
+        <v>4161.32</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46159</v>
+        <v>46150</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E47" s="16" t="n">
-        <v>331.55</v>
+        <v>2781.99</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46161</v>
+        <v>46150</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E48" s="16" t="n">
-        <v>4716.25</v>
+        <v>2154.44</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E49" s="16" t="n">
-        <v>1102.5</v>
+        <v>3399.66</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Não informado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46162</v>
+        <v>46151</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E50" s="16" t="n">
-        <v>4557.55</v>
+        <v>4823.6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2869,11 +2869,11 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46163</v>
+        <v>46152</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="E51" s="16" t="n">
-        <v>2087.64</v>
+        <v>58.37</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46163</v>
+        <v>46152</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2915,91 +2915,91 @@
         </is>
       </c>
       <c r="E52" s="16" t="n">
-        <v>1715.16</v>
+        <v>3413.61</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E53" s="16" t="n">
-        <v>3192.18</v>
+        <v>1546.22</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E54" s="16" t="n">
-        <v>3014.78</v>
+        <v>4089.32</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46165</v>
+        <v>46157</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E55" s="16" t="n">
-        <v>1428.46</v>
+        <v>2801.17</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3009,16 +3009,16 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46166</v>
+        <v>46159</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3027,45 +3027,45 @@
         </is>
       </c>
       <c r="E56" s="16" t="n">
-        <v>998.13</v>
+        <v>331.55</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E57" s="16" t="n">
-        <v>1230.8</v>
+        <v>4716.25</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3083,21 +3083,21 @@
         </is>
       </c>
       <c r="E58" s="16" t="n">
-        <v>1252.84</v>
+        <v>1102.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3107,30 +3107,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E59" s="16" t="n">
-        <v>266.05</v>
+        <v>4557.55</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E60" s="16" t="n">
-        <v>4181.88</v>
+        <v>1715.16</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3167,26 +3167,26 @@
         </is>
       </c>
       <c r="E61" s="16" t="n">
-        <v>4182.81</v>
+        <v>2087.64</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3195,21 +3195,21 @@
         </is>
       </c>
       <c r="E62" s="16" t="n">
-        <v>2223.81</v>
+        <v>3192.18</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46172</v>
+        <v>46164</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3219,11 +3219,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E63" s="16" t="n">
-        <v>4045.28</v>
+        <v>3014.78</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3233,25 +3233,25 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46172</v>
+        <v>46165</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E64" s="16" t="n">
-        <v>1151.05</v>
+        <v>1428.46</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3261,44 +3261,44 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46172</v>
+        <v>46166</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E65" s="16" t="n">
-        <v>3196.15</v>
+        <v>998.13</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46173</v>
+        <v>46168</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="E66" s="16" t="n">
-        <v>543.5700000000001</v>
+        <v>1252.84</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3317,16 +3317,16 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46173</v>
+        <v>46168</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3335,45 +3335,45 @@
         </is>
       </c>
       <c r="E67" s="16" t="n">
-        <v>1791.46</v>
+        <v>266.05</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Não informado</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E68" s="16" t="n">
-        <v>2025.01</v>
+        <v>1230.8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Não informado</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3391,54 +3391,54 @@
         </is>
       </c>
       <c r="E69" s="16" t="n">
-        <v>1699.88</v>
+        <v>4182.81</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="15" t="n">
-        <v>46178</v>
+        <v>46169</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E70" s="16" t="n">
-        <v>3355.92</v>
+        <v>4181.88</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="15" t="n">
-        <v>46178</v>
+        <v>46170</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3447,26 +3447,26 @@
         </is>
       </c>
       <c r="E71" s="16" t="n">
-        <v>2776.65</v>
+        <v>2223.81</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
-        <v>46179</v>
+        <v>46172</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3475,82 +3475,82 @@
         </is>
       </c>
       <c r="E72" s="16" t="n">
-        <v>1470.22</v>
+        <v>1151.05</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="15" t="n">
-        <v>46179</v>
+        <v>46172</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E73" s="16" t="n">
-        <v>3010.28</v>
+        <v>4045.28</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="15" t="n">
-        <v>46180</v>
+        <v>46172</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E74" s="16" t="n">
-        <v>2301.39</v>
+        <v>3196.15</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="15" t="n">
-        <v>46180</v>
+        <v>46173</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3559,54 +3559,54 @@
         </is>
       </c>
       <c r="E75" s="16" t="n">
-        <v>1761.15</v>
+        <v>543.5700000000001</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="15" t="n">
-        <v>46181</v>
+        <v>46173</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E76" s="16" t="n">
-        <v>647.25</v>
+        <v>1791.46</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="15" t="n">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E77" s="16" t="n">
-        <v>167.14</v>
+        <v>1430.69</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3625,16 +3625,16 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
-        <v>46181</v>
+        <v>46175</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E78" s="16" t="n">
-        <v>4903.53</v>
+        <v>4333.04</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3653,16 +3653,16 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E79" s="16" t="n">
-        <v>1615.08</v>
+        <v>849.83</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="15" t="n">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3699,35 +3699,35 @@
         </is>
       </c>
       <c r="E80" s="16" t="n">
-        <v>4141.82</v>
+        <v>2351.69</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="15" t="n">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E81" s="16" t="n">
-        <v>1667.26</v>
+        <v>4641.98</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3737,16 +3737,16 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n">
-        <v>46187</v>
+        <v>46178</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="E82" s="16" t="n">
-        <v>4119.47</v>
+        <v>3746.49</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3765,44 +3765,44 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n">
-        <v>46187</v>
+        <v>46179</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E83" s="16" t="n">
-        <v>1108.05</v>
+        <v>3010.28</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="15" t="n">
-        <v>46188</v>
+        <v>46179</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3811,26 +3811,26 @@
         </is>
       </c>
       <c r="E84" s="16" t="n">
-        <v>3135.13</v>
+        <v>1470.22</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
-        <v>46190</v>
+        <v>46180</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3839,35 +3839,35 @@
         </is>
       </c>
       <c r="E85" s="16" t="n">
-        <v>1528.13</v>
+        <v>3747.72</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="15" t="n">
-        <v>46191</v>
+        <v>46180</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E86" s="16" t="n">
-        <v>3002.22</v>
+        <v>465.54</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
-        <v>46191</v>
+        <v>46180</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E87" s="16" t="n">
-        <v>1036.12</v>
+        <v>1768.66</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3905,44 +3905,44 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E88" s="16" t="n">
-        <v>796.61</v>
+        <v>3212.75</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="15" t="n">
-        <v>46192</v>
+        <v>46182</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="E89" s="16" t="n">
-        <v>1720.63</v>
+        <v>112.63</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3961,44 +3961,44 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n">
-        <v>46192</v>
+        <v>46182</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E90" s="16" t="n">
-        <v>298.91</v>
+        <v>358.22</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Não informado</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="n">
-        <v>46192</v>
+        <v>46183</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4007,82 +4007,82 @@
         </is>
       </c>
       <c r="E91" s="16" t="n">
-        <v>3889.68</v>
+        <v>1417.42</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>46196</v>
+        <v>46183</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E92" s="16" t="n">
-        <v>215.15</v>
+        <v>2812.46</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>46199</v>
+        <v>46183</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E93" s="16" t="n">
-        <v>3351.32</v>
+        <v>1667.26</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>46199</v>
+        <v>46184</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4091,54 +4091,54 @@
         </is>
       </c>
       <c r="E94" s="16" t="n">
-        <v>3311.96</v>
+        <v>1258.78</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>46199</v>
+        <v>46185</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E95" s="16" t="n">
-        <v>855.14</v>
+        <v>367.93</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
-        <v>46200</v>
+        <v>46187</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4147,26 +4147,26 @@
         </is>
       </c>
       <c r="E96" s="16" t="n">
-        <v>4999.54</v>
+        <v>4119.47</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
-        <v>46201</v>
+        <v>46187</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4175,26 +4175,26 @@
         </is>
       </c>
       <c r="E97" s="16" t="n">
-        <v>2789.69</v>
+        <v>1108.05</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
-        <v>46202</v>
+        <v>46188</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E98" s="16" t="n">
-        <v>3854.56</v>
+        <v>3135.13</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4213,16 +4213,16 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n">
-        <v>46207</v>
+        <v>46190</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4231,45 +4231,45 @@
         </is>
       </c>
       <c r="E99" s="16" t="n">
-        <v>2324.87</v>
+        <v>1528.13</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
-        <v>46207</v>
+        <v>46191</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E100" s="16" t="n">
-        <v>999.61</v>
+        <v>1036.12</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
-        <v>46208</v>
+        <v>46191</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4287,26 +4287,26 @@
         </is>
       </c>
       <c r="E101" s="16" t="n">
-        <v>4161.32</v>
+        <v>3002.22</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="n">
-        <v>46208</v>
+        <v>46191</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="E102" s="16" t="n">
-        <v>2243.5</v>
+        <v>796.61</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4325,25 +4325,25 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
-        <v>46209</v>
+        <v>46192</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E103" s="16" t="n">
-        <v>3747.72</v>
+        <v>298.91</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4353,16 +4353,16 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n">
-        <v>46209</v>
+        <v>46192</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4371,21 +4371,21 @@
         </is>
       </c>
       <c r="E104" s="16" t="n">
-        <v>1768.66</v>
+        <v>3889.68</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="15" t="n">
-        <v>46209</v>
+        <v>46192</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4395,11 +4395,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E105" s="16" t="n">
-        <v>465.54</v>
+        <v>1720.63</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4409,16 +4409,16 @@
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
-        <v>46211</v>
+        <v>46196</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4427,26 +4427,26 @@
         </is>
       </c>
       <c r="E106" s="16" t="n">
-        <v>2095.58</v>
+        <v>215.15</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
-        <v>46211</v>
+        <v>46199</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4455,26 +4455,26 @@
         </is>
       </c>
       <c r="E107" s="16" t="n">
-        <v>1134.07</v>
+        <v>855.14</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Não informado</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
-        <v>46212</v>
+        <v>46199</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4483,54 +4483,54 @@
         </is>
       </c>
       <c r="E108" s="16" t="n">
-        <v>1852.9</v>
+        <v>3351.32</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
-        <v>46217</v>
+        <v>46199</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E109" s="16" t="n">
-        <v>4111.72</v>
+        <v>3311.96</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="15" t="n">
-        <v>46218</v>
+        <v>46200</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="E110" s="16" t="n">
-        <v>2273.58</v>
+        <v>4999.54</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4549,11 +4549,11 @@
     </row>
     <row r="111">
       <c r="A111" s="15" t="n">
-        <v>46218</v>
+        <v>46201</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4563,11 +4563,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E111" s="16" t="n">
-        <v>4836.1</v>
+        <v>2789.69</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4577,44 +4577,44 @@
     </row>
     <row r="112">
       <c r="A112" s="15" t="n">
-        <v>46219</v>
+        <v>46202</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E112" s="16" t="n">
-        <v>173.8</v>
+        <v>3854.56</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4623,49 +4623,49 @@
         </is>
       </c>
       <c r="E113" s="16" t="n">
-        <v>3152.4</v>
+        <v>1210.74</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="15" t="n">
-        <v>46220</v>
+        <v>46204</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E114" s="16" t="n">
-        <v>2466.74</v>
+        <v>172.69</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="15" t="n">
-        <v>46220</v>
+        <v>46206</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4675,30 +4675,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E115" s="16" t="n">
-        <v>2338.19</v>
+        <v>3351.12</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="n">
-        <v>46222</v>
+        <v>46209</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4707,54 +4707,54 @@
         </is>
       </c>
       <c r="E116" s="16" t="n">
-        <v>3452.56</v>
+        <v>2301.39</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="15" t="n">
-        <v>46222</v>
+        <v>46209</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E117" s="16" t="n">
-        <v>4927.28</v>
+        <v>1761.15</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="15" t="n">
-        <v>46222</v>
+        <v>46211</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4763,26 +4763,26 @@
         </is>
       </c>
       <c r="E118" s="16" t="n">
-        <v>933.91</v>
+        <v>3474.35</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Não informado</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="15" t="n">
-        <v>46222</v>
+        <v>46212</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="E119" s="16" t="n">
-        <v>2295.93</v>
+        <v>3096.8</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4801,16 +4801,16 @@
     </row>
     <row r="120">
       <c r="A120" s="15" t="n">
-        <v>46223</v>
+        <v>46213</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="E120" s="16" t="n">
-        <v>1806.38</v>
+        <v>4359.07</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4829,25 +4829,25 @@
     </row>
     <row r="121">
       <c r="A121" s="15" t="n">
-        <v>46224</v>
+        <v>46214</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E121" s="16" t="n">
-        <v>2351.92</v>
+        <v>816.24</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4857,16 +4857,16 @@
     </row>
     <row r="122">
       <c r="A122" s="15" t="n">
-        <v>46225</v>
+        <v>46214</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4875,26 +4875,26 @@
         </is>
       </c>
       <c r="E122" s="16" t="n">
-        <v>2551.77</v>
+        <v>3990.91</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="15" t="n">
-        <v>46226</v>
+        <v>46215</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4903,54 +4903,54 @@
         </is>
       </c>
       <c r="E123" s="16" t="n">
-        <v>298.58</v>
+        <v>4666.63</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="n">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E124" s="16" t="n">
-        <v>3783.45</v>
+        <v>4111.72</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="15" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4959,35 +4959,35 @@
         </is>
       </c>
       <c r="E125" s="16" t="n">
-        <v>1361.16</v>
+        <v>2273.58</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="15" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E126" s="16" t="n">
-        <v>2277.85</v>
+        <v>4836.1</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4997,16 +4997,16 @@
     </row>
     <row r="127">
       <c r="A127" s="15" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5015,54 +5015,54 @@
         </is>
       </c>
       <c r="E127" s="16" t="n">
-        <v>4410.28</v>
+        <v>3152.4</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="15" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E128" s="16" t="n">
-        <v>2497.17</v>
+        <v>173.8</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="15" t="n">
-        <v>46228</v>
+        <v>46220</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5071,35 +5071,35 @@
         </is>
       </c>
       <c r="E129" s="16" t="n">
-        <v>4904.83</v>
+        <v>2338.19</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="15" t="n">
-        <v>46228</v>
+        <v>46220</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E130" s="16" t="n">
-        <v>1235.29</v>
+        <v>2466.74</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5109,25 +5109,25 @@
     </row>
     <row r="131">
       <c r="A131" s="15" t="n">
-        <v>46228</v>
+        <v>46222</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E131" s="16" t="n">
-        <v>2468.46</v>
+        <v>3452.56</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5137,44 +5137,44 @@
     </row>
     <row r="132">
       <c r="A132" s="15" t="n">
-        <v>46229</v>
+        <v>46222</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E132" s="16" t="n">
-        <v>4846.53</v>
+        <v>933.91</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="15" t="n">
-        <v>46229</v>
+        <v>46222</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5183,26 +5183,26 @@
         </is>
       </c>
       <c r="E133" s="16" t="n">
-        <v>4632.53</v>
+        <v>4927.28</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="15" t="n">
-        <v>46229</v>
+        <v>46222</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5211,21 +5211,21 @@
         </is>
       </c>
       <c r="E134" s="16" t="n">
-        <v>3106.42</v>
+        <v>2295.93</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="15" t="n">
-        <v>46229</v>
+        <v>46223</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5235,39 +5235,39 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E135" s="16" t="n">
-        <v>512.27</v>
+        <v>1806.38</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="15" t="n">
-        <v>46231</v>
+        <v>46224</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E136" s="16" t="n">
-        <v>178.03</v>
+        <v>2351.92</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
     </row>
     <row r="137">
       <c r="A137" s="15" t="n">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5295,17 +5295,17 @@
         </is>
       </c>
       <c r="E137" s="16" t="n">
-        <v>648.97</v>
+        <v>2551.77</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="15" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5323,26 +5323,26 @@
         </is>
       </c>
       <c r="E138" s="16" t="n">
-        <v>197.5</v>
+        <v>3783.45</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="15" t="n">
-        <v>46235</v>
+        <v>46226</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5351,35 +5351,35 @@
         </is>
       </c>
       <c r="E139" s="16" t="n">
-        <v>412.64</v>
+        <v>1361.16</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="15" t="n">
-        <v>46239</v>
+        <v>46226</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E140" s="16" t="n">
-        <v>2154.44</v>
+        <v>298.58</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -5389,44 +5389,44 @@
     </row>
     <row r="141">
       <c r="A141" s="15" t="n">
-        <v>46239</v>
+        <v>46226</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E141" s="16" t="n">
-        <v>3399.66</v>
+        <v>2277.85</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="15" t="n">
-        <v>46239</v>
+        <v>46227</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5435,21 +5435,21 @@
         </is>
       </c>
       <c r="E142" s="16" t="n">
-        <v>2781.99</v>
+        <v>2497.17</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="15" t="n">
-        <v>46240</v>
+        <v>46227</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5463,54 +5463,54 @@
         </is>
       </c>
       <c r="E143" s="16" t="n">
-        <v>3212.75</v>
+        <v>4410.28</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="15" t="n">
-        <v>46241</v>
+        <v>46228</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E144" s="16" t="n">
-        <v>3474.35</v>
+        <v>4904.83</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="15" t="n">
-        <v>46243</v>
+        <v>46228</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5519,45 +5519,45 @@
         </is>
       </c>
       <c r="E145" s="16" t="n">
-        <v>2035.77</v>
+        <v>1235.29</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="15" t="n">
-        <v>46246</v>
+        <v>46228</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E146" s="16" t="n">
-        <v>3065.2</v>
+        <v>2468.46</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="15" t="n">
-        <v>46246</v>
+        <v>46229</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5575,54 +5575,54 @@
         </is>
       </c>
       <c r="E147" s="16" t="n">
-        <v>3978.99</v>
+        <v>512.27</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="15" t="n">
-        <v>46247</v>
+        <v>46229</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E148" s="16" t="n">
-        <v>4736.9</v>
+        <v>3106.42</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="15" t="n">
-        <v>46248</v>
+        <v>46229</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5631,26 +5631,26 @@
         </is>
       </c>
       <c r="E149" s="16" t="n">
-        <v>3900.07</v>
+        <v>4632.53</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="15" t="n">
-        <v>46248</v>
+        <v>46229</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5659,26 +5659,26 @@
         </is>
       </c>
       <c r="E150" s="16" t="n">
-        <v>806.55</v>
+        <v>4846.53</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="15" t="n">
-        <v>46249</v>
+        <v>46231</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5687,110 +5687,110 @@
         </is>
       </c>
       <c r="E151" s="16" t="n">
-        <v>3404.17</v>
+        <v>178.03</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="15" t="n">
-        <v>46250</v>
+        <v>46232</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E152" s="16" t="n">
-        <v>4312.46</v>
+        <v>648.97</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="15" t="n">
-        <v>46250</v>
+        <v>46234</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E153" s="16" t="n">
-        <v>1734.24</v>
+        <v>197.5</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="15" t="n">
-        <v>46250</v>
+        <v>46235</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E154" s="16" t="n">
-        <v>4361.12</v>
+        <v>412.64</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="15" t="n">
-        <v>46252</v>
+        <v>46236</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="E155" s="16" t="n">
-        <v>2933.42</v>
+        <v>1444.69</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -5809,16 +5809,16 @@
     </row>
     <row r="156">
       <c r="A156" s="15" t="n">
-        <v>46254</v>
+        <v>46236</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="E156" s="16" t="n">
-        <v>4986.76</v>
+        <v>4740.57</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="15" t="n">
-        <v>46256</v>
+        <v>46237</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5851,11 +5851,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E157" s="16" t="n">
-        <v>1364.79</v>
+        <v>4676.8</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -5865,11 +5865,11 @@
     </row>
     <row r="158">
       <c r="A158" s="15" t="n">
-        <v>46258</v>
+        <v>46240</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5879,58 +5879,58 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E158" s="16" t="n">
-        <v>3333.77</v>
+        <v>167.14</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="15" t="n">
-        <v>46259</v>
+        <v>46240</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E159" s="16" t="n">
-        <v>2334.17</v>
+        <v>4903.53</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="15" t="n">
-        <v>46262</v>
+        <v>46240</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5939,54 +5939,54 @@
         </is>
       </c>
       <c r="E160" s="16" t="n">
-        <v>4468.67</v>
+        <v>647.25</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="15" t="n">
-        <v>46262</v>
+        <v>46241</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E161" s="16" t="n">
-        <v>1359.11</v>
+        <v>2095.58</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="15" t="n">
-        <v>46262</v>
+        <v>46241</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5995,54 +5995,54 @@
         </is>
       </c>
       <c r="E162" s="16" t="n">
-        <v>4012.93</v>
+        <v>1134.07</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="15" t="n">
-        <v>46264</v>
+        <v>46243</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E163" s="16" t="n">
-        <v>4283.82</v>
+        <v>743.9</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="15" t="n">
-        <v>46265</v>
+        <v>46245</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -6051,49 +6051,49 @@
         </is>
       </c>
       <c r="E164" s="16" t="n">
-        <v>509.09</v>
+        <v>827.4299999999999</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="15" t="n">
-        <v>46269</v>
+        <v>46246</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E165" s="16" t="n">
-        <v>4890.83</v>
+        <v>3978.99</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="15" t="n">
-        <v>46270</v>
+        <v>46246</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6103,11 +6103,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E166" s="16" t="n">
-        <v>4823.6</v>
+        <v>3065.2</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
     </row>
     <row r="167">
       <c r="A167" s="15" t="n">
-        <v>46271</v>
+        <v>46247</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -6135,21 +6135,21 @@
         </is>
       </c>
       <c r="E167" s="16" t="n">
-        <v>358.22</v>
+        <v>4736.9</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Não informado</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="15" t="n">
-        <v>46271</v>
+        <v>46248</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6159,30 +6159,30 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E168" s="16" t="n">
-        <v>112.63</v>
+        <v>3900.07</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="15" t="n">
-        <v>46272</v>
+        <v>46248</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6191,21 +6191,21 @@
         </is>
       </c>
       <c r="E169" s="16" t="n">
-        <v>3096.8</v>
+        <v>806.55</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="15" t="n">
-        <v>46273</v>
+        <v>46249</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E170" s="16" t="n">
-        <v>743.9</v>
+        <v>3404.17</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="15" t="n">
-        <v>46278</v>
+        <v>46250</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6243,30 +6243,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E171" s="16" t="n">
-        <v>779.4</v>
+        <v>4361.12</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="15" t="n">
-        <v>46278</v>
+        <v>46250</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6275,17 +6275,17 @@
         </is>
       </c>
       <c r="E172" s="16" t="n">
-        <v>4155.27</v>
+        <v>1734.24</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="15" t="n">
-        <v>46278</v>
+        <v>46250</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -6303,21 +6303,21 @@
         </is>
       </c>
       <c r="E173" s="16" t="n">
-        <v>3537.63</v>
+        <v>4312.46</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="15" t="n">
-        <v>46279</v>
+        <v>46252</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6331,17 +6331,17 @@
         </is>
       </c>
       <c r="E174" s="16" t="n">
-        <v>1855.03</v>
+        <v>2933.42</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="15" t="n">
-        <v>46279</v>
+        <v>46254</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6359,26 +6359,26 @@
         </is>
       </c>
       <c r="E175" s="16" t="n">
-        <v>2915.65</v>
+        <v>4986.76</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="15" t="n">
-        <v>46281</v>
+        <v>46256</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6387,21 +6387,21 @@
         </is>
       </c>
       <c r="E176" s="16" t="n">
-        <v>1183.26</v>
+        <v>1364.79</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="15" t="n">
-        <v>46285</v>
+        <v>46258</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6415,35 +6415,35 @@
         </is>
       </c>
       <c r="E177" s="16" t="n">
-        <v>2268.46</v>
+        <v>3333.77</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="15" t="n">
-        <v>46287</v>
+        <v>46259</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E178" s="16" t="n">
-        <v>4856.84</v>
+        <v>2334.17</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -6453,16 +6453,16 @@
     </row>
     <row r="179">
       <c r="A179" s="15" t="n">
-        <v>46288</v>
+        <v>46262</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -6471,54 +6471,54 @@
         </is>
       </c>
       <c r="E179" s="16" t="n">
-        <v>2962.78</v>
+        <v>4468.67</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Não informado</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="15" t="n">
-        <v>46289</v>
+        <v>46262</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E180" s="16" t="n">
-        <v>4331.31</v>
+        <v>1359.11</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="15" t="n">
-        <v>46300</v>
+        <v>46262</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6527,54 +6527,54 @@
         </is>
       </c>
       <c r="E181" s="16" t="n">
-        <v>58.37</v>
+        <v>4012.93</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="15" t="n">
-        <v>46300</v>
+        <v>46264</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E182" s="16" t="n">
-        <v>3413.61</v>
+        <v>4283.82</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="15" t="n">
-        <v>46301</v>
+        <v>46265</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -6583,63 +6583,63 @@
         </is>
       </c>
       <c r="E183" s="16" t="n">
-        <v>2812.46</v>
+        <v>509.09</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="15" t="n">
-        <v>46301</v>
+        <v>46271</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E184" s="16" t="n">
-        <v>1417.42</v>
+        <v>4141.82</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="15" t="n">
-        <v>46302</v>
+        <v>46271</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E185" s="16" t="n">
-        <v>4359.07</v>
+        <v>1615.08</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6649,16 +6649,16 @@
     </row>
     <row r="186">
       <c r="A186" s="15" t="n">
-        <v>46304</v>
+        <v>46272</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6667,21 +6667,21 @@
         </is>
       </c>
       <c r="E186" s="16" t="n">
-        <v>3438.84</v>
+        <v>1852.9</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="15" t="n">
-        <v>46304</v>
+        <v>46273</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6691,30 +6691,30 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E187" s="16" t="n">
-        <v>3752.48</v>
+        <v>2035.77</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="15" t="n">
-        <v>46330</v>
+        <v>46275</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E188" s="16" t="n">
-        <v>3682.29</v>
+        <v>3438.84</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Atrasado</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="15" t="n">
-        <v>46330</v>
+        <v>46275</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="E189" s="16" t="n">
-        <v>2828.16</v>
+        <v>3752.48</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -6761,11 +6761,11 @@
     </row>
     <row r="190">
       <c r="A190" s="15" t="n">
-        <v>46330</v>
+        <v>46276</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6775,30 +6775,30 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E190" s="16" t="n">
-        <v>2378.98</v>
+        <v>3145.77</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="15" t="n">
-        <v>46330</v>
+        <v>46276</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6807,26 +6807,26 @@
         </is>
       </c>
       <c r="E191" s="16" t="n">
-        <v>4942.65</v>
+        <v>1736.49</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="15" t="n">
-        <v>46331</v>
+        <v>46278</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6835,35 +6835,35 @@
         </is>
       </c>
       <c r="E192" s="16" t="n">
-        <v>1546.22</v>
+        <v>3537.63</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="15" t="n">
-        <v>46332</v>
+        <v>46278</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E193" s="16" t="n">
-        <v>1258.78</v>
+        <v>4155.27</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -6873,44 +6873,44 @@
     </row>
     <row r="194">
       <c r="A194" s="15" t="n">
-        <v>46333</v>
+        <v>46278</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E194" s="16" t="n">
-        <v>3990.91</v>
+        <v>779.4</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="15" t="n">
-        <v>46333</v>
+        <v>46279</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="E195" s="16" t="n">
-        <v>816.24</v>
+        <v>1855.03</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
     </row>
     <row r="196">
       <c r="A196" s="15" t="n">
-        <v>46334</v>
+        <v>46279</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -6947,35 +6947,35 @@
         </is>
       </c>
       <c r="E196" s="16" t="n">
-        <v>827.4299999999999</v>
+        <v>2915.65</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Pago</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="15" t="n">
-        <v>46335</v>
+        <v>46281</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Saída</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="E197" s="16" t="n">
-        <v>3145.77</v>
+        <v>1183.26</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -6985,16 +6985,16 @@
     </row>
     <row r="198">
       <c r="A198" s="15" t="n">
-        <v>46335</v>
+        <v>46285</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -7003,54 +7003,54 @@
         </is>
       </c>
       <c r="E198" s="16" t="n">
-        <v>1736.49</v>
+        <v>2268.46</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="15" t="n">
-        <v>46360</v>
+        <v>46287</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E199" s="16" t="n">
-        <v>3383.15</v>
+        <v>4856.84</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="15" t="n">
-        <v>46362</v>
+        <v>46288</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -7059,26 +7059,26 @@
         </is>
       </c>
       <c r="E200" s="16" t="n">
-        <v>367.93</v>
+        <v>2962.78</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="15" t="n">
-        <v>46363</v>
+        <v>46289</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -7087,11 +7087,11 @@
         </is>
       </c>
       <c r="E201" s="16" t="n">
-        <v>4666.63</v>
+        <v>4331.31</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7133,7 +7133,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: Jan/2026 a Dec/2026 · valores somados a partir da aba Dados</t>
+          <t>Período: Mar/2026 a Sep/2026 · valores somados a partir da aba Dados</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -7170,7 +7170,7 @@
     </row>
     <row r="5">
       <c r="A5" s="17" t="n">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A5,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A5,1))</f>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
-        <v>46054</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A6,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A6,1))</f>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="B7" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A7,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A7,1))</f>
@@ -7233,7 +7233,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="B8" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A8,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A8,1))</f>
@@ -7254,7 +7254,7 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="n">
-        <v>46143</v>
+        <v>46204</v>
       </c>
       <c r="B9" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A9,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A9,1))</f>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
       <c r="B10" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A10,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A10,1))</f>
@@ -7296,7 +7296,7 @@
     </row>
     <row r="11">
       <c r="A11" s="17" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="B11" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A11,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A11,1))</f>
@@ -7316,136 +7316,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B12" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A12,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A12,1))</f>
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B12" s="19">
+        <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$A$2:$A$201,"&gt;="&amp;A12,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A12,1))</f>
+      <c r="C12" s="19">
+        <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="16">
-        <f>B12-C12</f>
+      <c r="D12" s="19">
+        <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="16">
-        <f>E11+D12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B13" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A13,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A13,1))</f>
-        <v/>
-      </c>
-      <c r="C13" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$A$2:$A$201,"&gt;="&amp;A13,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A13,1))</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>B13-C13</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>E12+D13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B14" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A14,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A14,1))</f>
-        <v/>
-      </c>
-      <c r="C14" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$A$2:$A$201,"&gt;="&amp;A14,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A14,1))</f>
-        <v/>
-      </c>
-      <c r="D14" s="16">
-        <f>B14-C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>E13+D14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B15" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A15,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A15,1))</f>
-        <v/>
-      </c>
-      <c r="C15" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$A$2:$A$201,"&gt;="&amp;A15,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A15,1))</f>
-        <v/>
-      </c>
-      <c r="D15" s="16">
-        <f>B15-C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="16">
-        <f>E14+D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B16" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$A$2:$A$201,"&gt;="&amp;A16,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A16,1))</f>
-        <v/>
-      </c>
-      <c r="C16" s="16">
-        <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$A$2:$A$201,"&gt;="&amp;A16,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A16,1))</f>
-        <v/>
-      </c>
-      <c r="D16" s="16">
-        <f>B16-C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="16">
-        <f>E15+D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B17" s="19">
-        <f>SUM(B5:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="19">
-        <f>SUM(C5:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="19">
-        <f>SUM(D5:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D16">
+  <conditionalFormatting sqref="D5:D11">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -7647,20 +7542,20 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46026</v>
+        <v>46109</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>2072.16</v>
+        <v>1195.81</v>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
@@ -7668,20 +7563,20 @@
         </is>
       </c>
       <c r="G12" s="15" t="n">
-        <v>46029</v>
+        <v>46109</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="J12" s="16" t="n">
-        <v>172.69</v>
+        <v>4177.04</v>
       </c>
       <c r="K12" s="31" t="inlineStr">
         <is>
@@ -7691,20 +7586,20 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46027</v>
+        <v>46111</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>4369.96</v>
+        <v>2789.13</v>
       </c>
       <c r="E13" s="30" t="inlineStr">
         <is>
@@ -7712,20 +7607,20 @@
         </is>
       </c>
       <c r="G13" s="15" t="n">
-        <v>46059</v>
+        <v>46118</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J13" s="16" t="n">
-        <v>4333.04</v>
+        <v>2025.01</v>
       </c>
       <c r="K13" s="30" t="inlineStr">
         <is>
@@ -7735,41 +7630,41 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46028</v>
+        <v>46113</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Venda de Serviço</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>2072.16</v>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>46119</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Saída - Cliente A</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Manutenção</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
-        <v>1430.69</v>
-      </c>
-      <c r="E14" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>46087</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Saída - Fornecedor Y</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
       <c r="J14" s="16" t="n">
-        <v>849.83</v>
+        <v>2324.87</v>
       </c>
       <c r="K14" s="30" t="inlineStr">
         <is>
@@ -7779,28 +7674,28 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46061</v>
+        <v>46119</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4740.57</v>
-      </c>
-      <c r="E15" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>999.61</v>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G15" s="15" t="n">
-        <v>46087</v>
+        <v>46129</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -7809,21 +7704,21 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="J15" s="16" t="n">
-        <v>2351.69</v>
-      </c>
-      <c r="K15" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4772.99</v>
+      </c>
+      <c r="K15" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46109</v>
+        <v>46123</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -7832,32 +7727,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1195.81</v>
-      </c>
-      <c r="E16" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>3682.29</v>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G16" s="15" t="n">
-        <v>46088</v>
+        <v>46130</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="J16" s="16" t="n">
-        <v>3351.12</v>
+        <v>4601.73</v>
       </c>
       <c r="K16" s="30" t="inlineStr">
         <is>
@@ -7867,20 +7762,20 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46111</v>
+        <v>46123</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>2789.13</v>
+        <v>2828.16</v>
       </c>
       <c r="E17" s="30" t="inlineStr">
         <is>
@@ -7888,64 +7783,64 @@
         </is>
       </c>
       <c r="G17" s="15" t="n">
-        <v>46089</v>
+        <v>46131</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="J17" s="16" t="n">
-        <v>4676.8</v>
-      </c>
-      <c r="K17" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>1561.63</v>
+      </c>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46128</v>
+        <v>46124</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2304.31</v>
-      </c>
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3383.15</v>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G18" s="15" t="n">
-        <v>46109</v>
+        <v>46136</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="J18" s="16" t="n">
-        <v>4177.04</v>
+        <v>4258.95</v>
       </c>
       <c r="K18" s="31" t="inlineStr">
         <is>
@@ -7955,41 +7850,41 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46129</v>
+        <v>46128</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3159.83</v>
-      </c>
-      <c r="E19" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>2304.31</v>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G19" s="15" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="J19" s="16" t="n">
-        <v>4772.99</v>
+        <v>2881.02</v>
       </c>
       <c r="K19" s="30" t="inlineStr">
         <is>
@@ -8003,16 +7898,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>2782.6</v>
+        <v>3159.83</v>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
@@ -8020,7 +7915,7 @@
         </is>
       </c>
       <c r="G20" s="15" t="n">
-        <v>46130</v>
+        <v>46146</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -8029,11 +7924,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J20" s="16" t="n">
-        <v>4601.73</v>
+        <v>3354.51</v>
       </c>
       <c r="K20" s="30" t="inlineStr">
         <is>
@@ -8043,41 +7938,41 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>916.59</v>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>2782.6</v>
+      </c>
+      <c r="E21" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G21" s="15" t="n">
-        <v>46131</v>
+        <v>46149</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="J21" s="16" t="n">
-        <v>1561.63</v>
+        <v>4161.32</v>
       </c>
       <c r="K21" s="31" t="inlineStr">
         <is>
@@ -8087,64 +7982,64 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46140</v>
+        <v>46133</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>2513.45</v>
-      </c>
-      <c r="E22" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>916.59</v>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G22" s="15" t="n">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J22" s="16" t="n">
-        <v>4258.95</v>
-      </c>
-      <c r="K22" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>2781.99</v>
+      </c>
+      <c r="K22" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46142</v>
+        <v>46140</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>4647.99</v>
+        <v>2513.45</v>
       </c>
       <c r="E23" s="30" t="inlineStr">
         <is>
@@ -8152,11 +8047,11 @@
         </is>
       </c>
       <c r="G23" s="15" t="n">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8165,74 +8060,74 @@
         </is>
       </c>
       <c r="J23" s="16" t="n">
-        <v>2881.02</v>
-      </c>
-      <c r="K23" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>58.37</v>
+      </c>
+      <c r="K23" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46148</v>
+        <v>46142</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>3746.49</v>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4647.99</v>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G24" s="15" t="n">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="J24" s="16" t="n">
-        <v>3354.51</v>
-      </c>
-      <c r="K24" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>4089.32</v>
+      </c>
+      <c r="K24" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46164</v>
+        <v>46143</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>3014.78</v>
+        <v>4369.96</v>
       </c>
       <c r="E25" s="30" t="inlineStr">
         <is>
@@ -8240,64 +8135,64 @@
         </is>
       </c>
       <c r="G25" s="15" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J25" s="16" t="n">
-        <v>4089.32</v>
-      </c>
-      <c r="K25" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4716.25</v>
+      </c>
+      <c r="K25" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46166</v>
+        <v>46149</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>2243.5</v>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>46162</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Saída - Fornecedor X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D26" s="16" t="n">
-        <v>998.13</v>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>46161</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Saída - Fornecedor Y</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Venda de Serviço</t>
-        </is>
-      </c>
       <c r="J26" s="16" t="n">
-        <v>4716.25</v>
+        <v>1102.5</v>
       </c>
       <c r="K26" s="30" t="inlineStr">
         <is>
@@ -8307,32 +8202,32 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46179</v>
+        <v>46164</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>3010.28</v>
-      </c>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3014.78</v>
+      </c>
+      <c r="E27" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -8341,7 +8236,7 @@
         </is>
       </c>
       <c r="J27" s="16" t="n">
-        <v>1102.5</v>
+        <v>2087.64</v>
       </c>
       <c r="K27" s="30" t="inlineStr">
         <is>
@@ -8351,7 +8246,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46181</v>
+        <v>46166</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -8360,11 +8255,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>647.25</v>
+        <v>998.13</v>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
@@ -8395,20 +8290,20 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>167.14</v>
+        <v>1430.69</v>
       </c>
       <c r="E29" s="30" t="inlineStr">
         <is>
@@ -8416,20 +8311,20 @@
         </is>
       </c>
       <c r="G29" s="15" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J29" s="16" t="n">
-        <v>2087.64</v>
+        <v>3192.18</v>
       </c>
       <c r="K29" s="30" t="inlineStr">
         <is>
@@ -8439,20 +8334,20 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46187</v>
+        <v>46178</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>4119.47</v>
+        <v>3746.49</v>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
@@ -8460,7 +8355,7 @@
         </is>
       </c>
       <c r="G30" s="15" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -8469,21 +8364,21 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="J30" s="16" t="n">
-        <v>3192.18</v>
-      </c>
-      <c r="K30" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>4182.81</v>
+      </c>
+      <c r="K30" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46191</v>
+        <v>46179</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -8492,11 +8387,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>796.61</v>
+        <v>3010.28</v>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
@@ -8527,20 +8422,20 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46192</v>
+        <v>46180</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>298.91</v>
+        <v>465.54</v>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
@@ -8548,20 +8443,20 @@
         </is>
       </c>
       <c r="G32" s="15" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J32" s="16" t="n">
-        <v>4182.81</v>
+        <v>2223.81</v>
       </c>
       <c r="K32" s="31" t="inlineStr">
         <is>
@@ -8571,51 +8466,51 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46192</v>
+        <v>46183</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
-        <v>3889.68</v>
-      </c>
-      <c r="E33" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>1417.42</v>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G33" s="15" t="n">
-        <v>46170</v>
+        <v>46172</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="J33" s="16" t="n">
-        <v>2223.81</v>
-      </c>
-      <c r="K33" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4045.28</v>
+      </c>
+      <c r="K33" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46199</v>
+        <v>46183</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -8624,15 +8519,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>3351.32</v>
-      </c>
-      <c r="E34" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>2812.46</v>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G34" s="15" t="n">
@@ -8640,16 +8535,16 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="J34" s="16" t="n">
-        <v>4045.28</v>
+        <v>3196.15</v>
       </c>
       <c r="K34" s="30" t="inlineStr">
         <is>
@@ -8659,20 +8554,20 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46199</v>
+        <v>46185</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>3311.96</v>
+        <v>367.93</v>
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
@@ -8680,20 +8575,20 @@
         </is>
       </c>
       <c r="G35" s="15" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J35" s="16" t="n">
-        <v>3196.15</v>
+        <v>1791.46</v>
       </c>
       <c r="K35" s="30" t="inlineStr">
         <is>
@@ -8703,7 +8598,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46207</v>
+        <v>46187</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -8712,11 +8607,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>999.61</v>
+        <v>4119.47</v>
       </c>
       <c r="E36" s="31" t="inlineStr">
         <is>
@@ -8724,20 +8619,20 @@
         </is>
       </c>
       <c r="G36" s="15" t="n">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J36" s="16" t="n">
-        <v>1791.46</v>
+        <v>4333.04</v>
       </c>
       <c r="K36" s="30" t="inlineStr">
         <is>
@@ -8747,20 +8642,20 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46208</v>
+        <v>46191</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
-        <v>2243.5</v>
+        <v>796.61</v>
       </c>
       <c r="E37" s="31" t="inlineStr">
         <is>
@@ -8768,20 +8663,20 @@
         </is>
       </c>
       <c r="G37" s="15" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="J37" s="16" t="n">
-        <v>2025.01</v>
+        <v>849.83</v>
       </c>
       <c r="K37" s="30" t="inlineStr">
         <is>
@@ -8791,20 +8686,20 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46209</v>
+        <v>46192</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>465.54</v>
+        <v>298.91</v>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
@@ -8812,20 +8707,20 @@
         </is>
       </c>
       <c r="G38" s="15" t="n">
-        <v>46179</v>
+        <v>46176</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="J38" s="16" t="n">
-        <v>1470.22</v>
+        <v>2351.69</v>
       </c>
       <c r="K38" s="31" t="inlineStr">
         <is>
@@ -8835,32 +8730,32 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46212</v>
+        <v>46192</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
-        <v>1852.9</v>
-      </c>
-      <c r="E39" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3889.68</v>
+      </c>
+      <c r="E39" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G39" s="15" t="n">
-        <v>46180</v>
+        <v>46179</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -8869,7 +8764,7 @@
         </is>
       </c>
       <c r="J39" s="16" t="n">
-        <v>1761.15</v>
+        <v>1470.22</v>
       </c>
       <c r="K39" s="31" t="inlineStr">
         <is>
@@ -8879,41 +8774,41 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46218</v>
+        <v>46199</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>4836.1</v>
-      </c>
-      <c r="E40" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3311.96</v>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G40" s="15" t="n">
-        <v>46181</v>
+        <v>46180</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J40" s="16" t="n">
-        <v>4903.53</v>
+        <v>3747.72</v>
       </c>
       <c r="K40" s="30" t="inlineStr">
         <is>
@@ -8923,51 +8818,51 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46220</v>
+        <v>46199</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
-        <v>2338.19</v>
-      </c>
-      <c r="E41" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3351.32</v>
+      </c>
+      <c r="E41" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G41" s="15" t="n">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J41" s="16" t="n">
-        <v>1615.08</v>
-      </c>
-      <c r="K41" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3212.75</v>
+      </c>
+      <c r="K41" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46222</v>
+        <v>46213</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -8980,7 +8875,7 @@
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>3452.56</v>
+        <v>4359.07</v>
       </c>
       <c r="E42" s="31" t="inlineStr">
         <is>
@@ -8992,16 +8887,16 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="J42" s="16" t="n">
-        <v>4141.82</v>
+        <v>112.63</v>
       </c>
       <c r="K42" s="30" t="inlineStr">
         <is>
@@ -9011,24 +8906,24 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46222</v>
+        <v>46218</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D43" s="16" t="n">
-        <v>4927.28</v>
-      </c>
-      <c r="E43" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>4836.1</v>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G43" s="15" t="n">
@@ -9055,20 +8950,20 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>1806.38</v>
+        <v>2338.19</v>
       </c>
       <c r="E44" s="31" t="inlineStr">
         <is>
@@ -9099,20 +8994,20 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D45" s="16" t="n">
-        <v>2351.92</v>
+        <v>3452.56</v>
       </c>
       <c r="E45" s="31" t="inlineStr">
         <is>
@@ -9143,24 +9038,24 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46226</v>
+        <v>46222</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>1361.16</v>
-      </c>
-      <c r="E46" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4927.28</v>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G46" s="15" t="n">
@@ -9187,24 +9082,24 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46229</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D47" s="16" t="n">
-        <v>4846.53</v>
-      </c>
-      <c r="E47" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>1806.38</v>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G47" s="15" t="n">
@@ -9231,24 +9126,24 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46229</v>
+        <v>46224</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>3106.42</v>
-      </c>
-      <c r="E48" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>2351.92</v>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G48" s="15" t="n">
@@ -9275,11 +9170,11 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9288,7 +9183,7 @@
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>197.5</v>
+        <v>1361.16</v>
       </c>
       <c r="E49" s="31" t="inlineStr">
         <is>
@@ -9319,32 +9214,32 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46248</v>
+        <v>46229</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>3900.07</v>
-      </c>
-      <c r="E50" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3106.42</v>
+      </c>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G50" s="15" t="n">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -9353,38 +9248,38 @@
         </is>
       </c>
       <c r="J50" s="16" t="n">
-        <v>2324.87</v>
-      </c>
-      <c r="K50" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>172.69</v>
+      </c>
+      <c r="K50" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46248</v>
+        <v>46229</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>806.55</v>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4846.53</v>
+      </c>
+      <c r="E51" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G51" s="15" t="n">
-        <v>46208</v>
+        <v>46206</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -9393,34 +9288,34 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="J51" s="16" t="n">
-        <v>4161.32</v>
-      </c>
-      <c r="K51" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3351.12</v>
+      </c>
+      <c r="K51" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46250</v>
+        <v>46234</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>4312.46</v>
+        <v>197.5</v>
       </c>
       <c r="E52" s="31" t="inlineStr">
         <is>
@@ -9432,26 +9327,26 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="J52" s="16" t="n">
-        <v>3747.72</v>
-      </c>
-      <c r="K52" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>1761.15</v>
+      </c>
+      <c r="K52" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46256</v>
+        <v>46236</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -9460,11 +9355,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D53" s="16" t="n">
-        <v>1364.79</v>
+        <v>4740.57</v>
       </c>
       <c r="E53" s="30" t="inlineStr">
         <is>
@@ -9472,20 +9367,20 @@
         </is>
       </c>
       <c r="G53" s="15" t="n">
-        <v>46211</v>
+        <v>46214</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="J53" s="16" t="n">
-        <v>2095.58</v>
+        <v>816.24</v>
       </c>
       <c r="K53" s="31" t="inlineStr">
         <is>
@@ -9495,64 +9390,64 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46264</v>
+        <v>46240</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor X</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>647.25</v>
+      </c>
+      <c r="E54" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Saída - Cliente C</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>Salário</t>
         </is>
       </c>
-      <c r="D54" s="16" t="n">
-        <v>4283.82</v>
-      </c>
-      <c r="E54" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="G54" s="15" t="n">
-        <v>46211</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Saída - Fornecedor Y</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Salário</t>
-        </is>
-      </c>
       <c r="J54" s="16" t="n">
-        <v>1134.07</v>
-      </c>
-      <c r="K54" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3990.91</v>
+      </c>
+      <c r="K54" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46265</v>
+        <v>46240</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>509.09</v>
+        <v>167.14</v>
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
@@ -9560,43 +9455,43 @@
         </is>
       </c>
       <c r="G55" s="15" t="n">
-        <v>46217</v>
+        <v>46215</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="J55" s="16" t="n">
-        <v>4111.72</v>
-      </c>
-      <c r="K55" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4666.63</v>
+      </c>
+      <c r="K55" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46278</v>
+        <v>46248</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Entrada - Cliente B</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>779.4</v>
+        <v>3900.07</v>
       </c>
       <c r="E56" s="31" t="inlineStr">
         <is>
@@ -9604,20 +9499,20 @@
         </is>
       </c>
       <c r="G56" s="15" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J56" s="16" t="n">
-        <v>3152.4</v>
+        <v>4111.72</v>
       </c>
       <c r="K56" s="31" t="inlineStr">
         <is>
@@ -9627,32 +9522,32 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46278</v>
+        <v>46248</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D57" s="16" t="n">
-        <v>3537.63</v>
-      </c>
-      <c r="E57" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>806.55</v>
+      </c>
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G57" s="15" t="n">
-        <v>46222</v>
+        <v>46219</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -9661,7 +9556,7 @@
         </is>
       </c>
       <c r="J57" s="16" t="n">
-        <v>933.91</v>
+        <v>3152.4</v>
       </c>
       <c r="K57" s="31" t="inlineStr">
         <is>
@@ -9671,41 +9566,41 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46279</v>
+        <v>46250</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Fornecedor</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>4312.46</v>
+      </c>
+      <c r="E58" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>46222</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Saída - Cliente A</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>Aluguel</t>
         </is>
       </c>
-      <c r="D58" s="16" t="n">
-        <v>2915.65</v>
-      </c>
-      <c r="E58" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="G58" s="15" t="n">
-        <v>46225</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Saída - Cliente A</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Aluguel</t>
-        </is>
-      </c>
       <c r="J58" s="16" t="n">
-        <v>2551.77</v>
+        <v>933.91</v>
       </c>
       <c r="K58" s="31" t="inlineStr">
         <is>
@@ -9715,41 +9610,41 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46281</v>
+        <v>46256</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>1364.79</v>
+      </c>
+      <c r="E59" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>46225</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Saída - Cliente A</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>Aluguel</t>
         </is>
       </c>
-      <c r="D59" s="16" t="n">
-        <v>1183.26</v>
-      </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
-        </is>
-      </c>
-      <c r="G59" s="15" t="n">
-        <v>46226</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Saída - Fornecedor Z</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Salário</t>
-        </is>
-      </c>
       <c r="J59" s="16" t="n">
-        <v>2277.85</v>
+        <v>2551.77</v>
       </c>
       <c r="K59" s="31" t="inlineStr">
         <is>
@@ -9759,41 +9654,41 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46288</v>
+        <v>46264</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Fornecedor X</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D60" s="16" t="n">
-        <v>2962.78</v>
-      </c>
-      <c r="E60" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4283.82</v>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G60" s="15" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J60" s="16" t="n">
-        <v>2497.17</v>
+        <v>2277.85</v>
       </c>
       <c r="K60" s="31" t="inlineStr">
         <is>
@@ -9803,41 +9698,41 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46301</v>
+        <v>46265</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Y</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="D61" s="16" t="n">
-        <v>2812.46</v>
-      </c>
-      <c r="E61" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>509.09</v>
+      </c>
+      <c r="E61" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G61" s="15" t="n">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="J61" s="16" t="n">
-        <v>2468.46</v>
+        <v>2497.17</v>
       </c>
       <c r="K61" s="31" t="inlineStr">
         <is>
@@ -9847,20 +9742,20 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46301</v>
+        <v>46272</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="D62" s="16" t="n">
-        <v>1417.42</v>
+        <v>1852.9</v>
       </c>
       <c r="E62" s="31" t="inlineStr">
         <is>
@@ -9868,7 +9763,7 @@
         </is>
       </c>
       <c r="G62" s="15" t="n">
-        <v>46231</v>
+        <v>46228</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -9877,11 +9772,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J62" s="16" t="n">
-        <v>178.03</v>
+        <v>2468.46</v>
       </c>
       <c r="K62" s="31" t="inlineStr">
         <is>
@@ -9891,11 +9786,11 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46302</v>
+        <v>46275</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9904,51 +9799,51 @@
         </is>
       </c>
       <c r="D63" s="16" t="n">
-        <v>4359.07</v>
-      </c>
-      <c r="E63" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>3752.48</v>
+      </c>
+      <c r="E63" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="G63" s="15" t="n">
-        <v>46239</v>
+        <v>46231</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="J63" s="16" t="n">
-        <v>2781.99</v>
-      </c>
-      <c r="K63" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>178.03</v>
+      </c>
+      <c r="K63" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46304</v>
+        <v>46278</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Fornecedor Z</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="D64" s="16" t="n">
-        <v>3752.48</v>
+        <v>3537.63</v>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
@@ -9956,7 +9851,7 @@
         </is>
       </c>
       <c r="G64" s="15" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -9965,11 +9860,11 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="J64" s="16" t="n">
-        <v>3212.75</v>
+        <v>4676.8</v>
       </c>
       <c r="K64" s="30" t="inlineStr">
         <is>
@@ -9979,20 +9874,20 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46330</v>
+        <v>46278</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente B</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="D65" s="16" t="n">
-        <v>3682.29</v>
+        <v>779.4</v>
       </c>
       <c r="E65" s="31" t="inlineStr">
         <is>
@@ -10000,43 +9895,43 @@
         </is>
       </c>
       <c r="G65" s="15" t="n">
-        <v>46243</v>
+        <v>46240</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="J65" s="16" t="n">
-        <v>2035.77</v>
-      </c>
-      <c r="K65" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4903.53</v>
+      </c>
+      <c r="K65" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46330</v>
+        <v>46279</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Entrada - Fornecedor Z</t>
+          <t>Entrada - Fornecedor Y</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="D66" s="16" t="n">
-        <v>2828.16</v>
+        <v>2915.65</v>
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
@@ -10044,34 +9939,34 @@
         </is>
       </c>
       <c r="G66" s="15" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J66" s="16" t="n">
-        <v>3978.99</v>
-      </c>
-      <c r="K66" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>2095.58</v>
+      </c>
+      <c r="K66" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46360</v>
+        <v>46281</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Entrada - Cliente A</t>
+          <t>Entrada - Cliente C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10080,28 +9975,28 @@
         </is>
       </c>
       <c r="D67" s="16" t="n">
-        <v>3383.15</v>
-      </c>
-      <c r="E67" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>1183.26</v>
+      </c>
+      <c r="E67" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G67" s="15" t="n">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Y</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J67" s="16" t="n">
-        <v>4736.9</v>
+        <v>1134.07</v>
       </c>
       <c r="K67" s="31" t="inlineStr">
         <is>
@@ -10111,41 +10006,41 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
-        <v>46362</v>
+        <v>46288</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Entrada - Cliente C</t>
+          <t>Entrada - Cliente A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Imposto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D68" s="16" t="n">
-        <v>367.93</v>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>2962.78</v>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
       <c r="G68" s="15" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Saída - Cliente A</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Venda de Serviço</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="J68" s="16" t="n">
-        <v>3404.17</v>
+        <v>3978.99</v>
       </c>
       <c r="K68" s="30" t="inlineStr">
         <is>
@@ -10155,30 +10050,30 @@
     </row>
     <row r="69">
       <c r="G69" s="15" t="n">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="J69" s="16" t="n">
-        <v>1734.24</v>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>4736.9</v>
+      </c>
+      <c r="K69" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="G70" s="15" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -10191,7 +10086,7 @@
         </is>
       </c>
       <c r="J70" s="16" t="n">
-        <v>4361.12</v>
+        <v>3404.17</v>
       </c>
       <c r="K70" s="30" t="inlineStr">
         <is>
@@ -10201,43 +10096,43 @@
     </row>
     <row r="71">
       <c r="G71" s="15" t="n">
-        <v>46258</v>
+        <v>46250</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="J71" s="16" t="n">
-        <v>3333.77</v>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>1734.24</v>
+      </c>
+      <c r="K71" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="G72" s="15" t="n">
-        <v>46271</v>
+        <v>46250</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor X</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J72" s="16" t="n">
-        <v>112.63</v>
+        <v>4361.12</v>
       </c>
       <c r="K72" s="30" t="inlineStr">
         <is>
@@ -10247,20 +10142,20 @@
     </row>
     <row r="73">
       <c r="G73" s="15" t="n">
-        <v>46279</v>
+        <v>46258</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Fornecedor</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J73" s="16" t="n">
-        <v>1855.03</v>
+        <v>3333.77</v>
       </c>
       <c r="K73" s="31" t="inlineStr">
         <is>
@@ -10270,43 +10165,43 @@
     </row>
     <row r="74">
       <c r="G74" s="15" t="n">
-        <v>46289</v>
+        <v>46271</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="J74" s="16" t="n">
-        <v>4331.31</v>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>4141.82</v>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="G75" s="15" t="n">
-        <v>46300</v>
+        <v>46271</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Z</t>
+          <t>Saída - Cliente A</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Venda de Serviço</t>
         </is>
       </c>
       <c r="J75" s="16" t="n">
-        <v>58.37</v>
+        <v>1615.08</v>
       </c>
       <c r="K75" s="31" t="inlineStr">
         <is>
@@ -10316,30 +10211,30 @@
     </row>
     <row r="76">
       <c r="G76" s="15" t="n">
-        <v>46333</v>
+        <v>46273</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Saída - Cliente C</t>
+          <t>Saída - Cliente B</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Imposto</t>
         </is>
       </c>
       <c r="J76" s="16" t="n">
-        <v>3990.91</v>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>2035.77</v>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="G77" s="15" t="n">
-        <v>46333</v>
+        <v>46276</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -10348,11 +10243,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Salário</t>
         </is>
       </c>
       <c r="J77" s="16" t="n">
-        <v>816.24</v>
+        <v>3145.77</v>
       </c>
       <c r="K77" s="31" t="inlineStr">
         <is>
@@ -10362,30 +10257,30 @@
     </row>
     <row r="78">
       <c r="G78" s="15" t="n">
-        <v>46335</v>
+        <v>46276</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Saída - Cliente B</t>
+          <t>Saída - Cliente C</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Salário</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="J78" s="16" t="n">
-        <v>3145.77</v>
-      </c>
-      <c r="K78" s="31" t="inlineStr">
-        <is>
-          <t>Atrasado</t>
+        <v>1736.49</v>
+      </c>
+      <c r="K78" s="30" t="inlineStr">
+        <is>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="G79" s="15" t="n">
-        <v>46335</v>
+        <v>46279</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -10394,38 +10289,38 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fornecedor</t>
         </is>
       </c>
       <c r="J79" s="16" t="n">
-        <v>1736.49</v>
-      </c>
-      <c r="K79" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>1855.03</v>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="G80" s="15" t="n">
-        <v>46363</v>
+        <v>46289</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Saída - Fornecedor Y</t>
+          <t>Saída - Fornecedor Z</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="J80" s="16" t="n">
-        <v>4666.63</v>
-      </c>
-      <c r="K80" s="30" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+        <v>4331.31</v>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>Atrasado</t>
         </is>
       </c>
     </row>
